--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-29T07:23:21+00:00</t>
+    <t>2024-07-01T07:47:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T07:47:51+00:00</t>
+    <t>2024-07-01T18:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T18:04:04+00:00</t>
+    <t>2024-07-01T19:43:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:43:16+00:00</t>
+    <t>2024-07-01T19:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:47:03+00:00</t>
+    <t>2024-07-08T21:31:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T21:31:51+00:00</t>
+    <t>2024-07-13T00:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-13T00:07:23+00:00</t>
+    <t>2024-07-22T01:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-22T01:54:40+00:00</t>
+    <t>2024-08-18T18:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T18:57:20+00:00</t>
+    <t>2024-08-18T19:14:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T19:14:17+00:00</t>
+    <t>2024-10-17T13:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T13:36:11+00:00</t>
+    <t>2024-10-30T19:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T19:02:49+00:00</t>
+    <t>2024-11-07T20:59:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T20:59:16+00:00</t>
+    <t>2024-12-06T22:28:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T22:28:12+00:00</t>
+    <t>2024-12-30T06:20:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T06:20:40+00:00</t>
+    <t>2025-01-13T15:35:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T15:35:56+00:00</t>
+    <t>2025-01-13T20:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -29,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T20:12:32+00:00</t>
+    <t>2025-01-30T04:55:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,6 +97,27 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>HIV.B.DE202</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>HIV.B.DE203</t>
+  </si>
+  <si>
+    <t>Severe</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://smart.who.int/hiv/CodeSystem/HIVConcepts</t>
   </si>
 </sst>
 </file>
@@ -355,4 +377,58 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T04:55:08+00:00</t>
+    <t>2025-01-31T22:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T22:08:22+00:00</t>
+    <t>2025-02-01T06:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T06:47:49+00:00</t>
+    <t>2025-02-01T23:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T23:07:45+00:00</t>
+    <t>2025-02-01T23:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.4.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T23:40:00+00:00</t>
+    <t>2025-02-02T03:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-HIV.B.DE201.xlsx
+++ b/ValueSet-HIV.B.DE201.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-02T03:11:41+00:00</t>
+    <t>2025-03-10T17:41:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
